--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.143.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.143.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.143.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.143.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.143.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.143.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0143.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0143.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,26 +601,34 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: (Pray subpenaÃ¦na.)</t>
+          <t>L114: stray/suspicious non-ASCII glyph(s): U+5305 CJK UNIFIED IDEOGRAPH-5305 | isolated marker/symbol line :: 包</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: has since the â€” day of --------------------- committed</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]136</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]136</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L8: isolated marker/symbol line :: 2</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]136</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L12: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: has since the â€” day of --------------------- committed</t>
+          <t>L12: punctuation artifact: double/multiple hyphen :: has since the — day of --------------------- committed</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -657,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -666,14 +674,10 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” day of â€”</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------â€” d</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: mained out €</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -687,15 +691,11 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------â€” d</t>
+          <t>L41: punctuation artifact: double/multiple hyphen :: --------— d</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr">
-        <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --------â€” d</t>
-        </is>
-      </c>
+      <c r="S3" s="1" t="inlineStr"/>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” conces:</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: parenthesis/punctuation debris :: (Pray subpana.).•</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -774,12 +774,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -789,11 +789,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: county of â€”</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -805,7 +801,7 @@
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: parenthesis/punctuation debris :: (Pray subpana.).â€¢</t>
+          <t>L84: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: parenthesis/punctuation debris :: (Pray subpana.).•</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
@@ -840,11 +836,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” payable</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -856,7 +848,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: the .â€” ; ----------day of ------until the present time</t>
+          <t>L100: punctuation artifact: double/multiple hyphen :: the .— ; ----------day of ------until the present time</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -891,16 +883,12 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: mained out â‚¬</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: Â£</t>
+          <t>L80: isolated marker/symbol line :: £</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr"/>
@@ -938,16 +926,12 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Â£â€” whicl</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: Â£</t>
+          <t>L81: isolated marker/symbol line :: £</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr"/>
@@ -985,11 +969,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L84: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: parenthesis/punctuation debris :: (Pray subpana.).â€¢</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1017,12 +997,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1032,14 +1012,14 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: may be), and in possession of lot number â€” ___and</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L114: stray/suspicious non-ASCII glyph(s): U+5305 CJK UNIFIED IDEOGRAPH-5305 | isolated marker/symbol line :: 包</t>
+        </is>
+      </c>
       <c r="O10" s="1" t="inlineStr"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
@@ -1065,7 +1045,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1075,11 +1055,7 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: the .â€” ; ----------day of ------until the present time</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr"/>
@@ -1103,12 +1079,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1186,7 +1162,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
